--- a/artfynd/A 54208-2025 artfynd.xlsx
+++ b/artfynd/A 54208-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,41 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>109161346</v>
+        <v>109162876</v>
       </c>
       <c r="B2" t="n">
-        <v>98974</v>
+        <v>99195</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>223597</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr"/>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>1900 m SO-SSO om bäckuppfödet från södra Hannuvuoma, Nb</t>
+          <t>1800 m SO-SSO om bäckuppflödet från södra Hannuvuoma, Nb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>849793</v>
+        <v>849791</v>
       </c>
       <c r="R2" t="n">
-        <v>7439213</v>
+        <v>7439413</v>
       </c>
       <c r="S2" t="n">
         <v>100</v>
@@ -760,7 +764,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>vägkant</t>
+          <t>blandskog i sluttning</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -782,32 +786,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>109162876</v>
+        <v>120877631</v>
       </c>
       <c r="B3" t="n">
-        <v>99054</v>
+        <v>106358</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>221157</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåbär</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Vaccinium myrtillus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -893,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>109173605</v>
+        <v>121055340</v>
       </c>
       <c r="B4" t="n">
-        <v>97920</v>
+        <v>107695</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -904,21 +908,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>224362</v>
+        <v>221705</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Nordlummer</t>
+          <t>Ängskovall</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum subsp. alpestre</t>
+          <t>Melampyrum pratense</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hartm.) Á. Löve &amp; D. Löve</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -1004,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>109189739</v>
+        <v>121053393</v>
       </c>
       <c r="B5" t="n">
-        <v>97926</v>
+        <v>106309</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1015,30 +1019,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>224358</v>
+        <v>221725</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vanlig plattlummer</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum subsp. complanatum</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr"/>
+          <t>Moneses uniflora</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>1800 m SO-SSO om bäckuppflödet från södra Hannuvuoma, Nb</t>
+          <t>1900 m SO-SSO om bäckuppfödet från södra Hannuvuoma, Nb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>849791</v>
+        <v>849793</v>
       </c>
       <c r="R5" t="n">
-        <v>7439413</v>
+        <v>7439213</v>
       </c>
       <c r="S5" t="n">
         <v>100</v>
@@ -1089,7 +1097,7 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>blandskog i sluttning</t>
+          <t>vägkant</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1111,10 +1119,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121053393</v>
+        <v>109161346</v>
       </c>
       <c r="B6" t="n">
-        <v>106163</v>
+        <v>99115</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1122,23 +1130,19 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221725</v>
+        <v>223597</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Jungfru marie nycklar</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>(L.) A. Gray</t>
-        </is>
-      </c>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1215,6 +1219,224 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr">
+        <is>
+          <t>Norrbottens flora 2010</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>109189739</v>
+      </c>
+      <c r="B7" t="n">
+        <v>98067</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>224358</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Vanlig plattlummer</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum subsp. complanatum</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>1800 m SO-SSO om bäckuppflödet från södra Hannuvuoma, Nb</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>849791</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7439413</v>
+      </c>
+      <c r="S7" t="n">
+        <v>100</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Korpilombolo</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2000-07-24</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2000-07-24</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Norrbottens flora - 2010.</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>blandskog i sluttning</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Mora Aronsson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Ulf Zethraeus, Tage Brännvall</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Norrbottens flora 2010</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>109173605</v>
+      </c>
+      <c r="B8" t="n">
+        <v>98061</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>224362</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Nordlummer</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum subsp. alpestre</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Hartm.) Á. Löve &amp; D. Löve</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>1800 m SO-SSO om bäckuppflödet från södra Hannuvuoma, Nb</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>849791</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7439413</v>
+      </c>
+      <c r="S8" t="n">
+        <v>100</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Korpilombolo</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2000-07-24</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2000-07-24</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Norrbottens flora - 2010.</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>blandskog i sluttning</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Mora Aronsson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Ulf Zethraeus, Tage Brännvall</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
         <is>
           <t>Norrbottens flora 2010</t>
         </is>

--- a/artfynd/A 54208-2025 artfynd.xlsx
+++ b/artfynd/A 54208-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -783,6 +788,11 @@
           <t>Norrbottens flora 2010</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109162876</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -894,6 +904,11 @@
           <t>Norrbottens flora 2010</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120877631</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1005,6 +1020,11 @@
           <t>Norrbottens flora 2010</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121055340</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1116,6 +1136,11 @@
           <t>Norrbottens flora 2010</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121053393</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1223,6 +1248,11 @@
           <t>Norrbottens flora 2010</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109161346</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1330,6 +1360,11 @@
           <t>Norrbottens flora 2010</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109189739</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1441,8 +1476,22 @@
           <t>Norrbottens flora 2010</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109173605</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>